--- a/data/trans_orig/POLIPATOLOGIA_5-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/POLIPATOLOGIA_5-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas en 2007</t>
+          <t>Población con cinco o más enfermedades crónicas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3552</t>
+          <t>3380</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13488</t>
+          <t>13394</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9392</t>
+          <t>9004</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26149</t>
+          <t>26001</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14910</t>
+          <t>15362</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34178</t>
+          <t>34022</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>259522</t>
+          <t>259616</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>269458</t>
+          <t>269630</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>234689</t>
+          <t>234837</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>251446</t>
+          <t>251834</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>499670</t>
+          <t>499826</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>518938</t>
+          <t>518486</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,12%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8412</t>
+          <t>8744</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25791</t>
+          <t>24968</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45508</t>
+          <t>45169</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72581</t>
+          <t>72848</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>58340</t>
+          <t>57344</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>91043</t>
+          <t>91365</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>467284</t>
+          <t>468107</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>484663</t>
+          <t>484331</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>431368</t>
+          <t>431101</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>458441</t>
+          <t>458780</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>905981</t>
+          <t>905659</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>938684</t>
+          <t>939680</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,25%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>943</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9259</t>
+          <t>8603</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3434</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16063</t>
+          <t>15449</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6491</t>
+          <t>6349</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19938</t>
+          <t>20493</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>309587</t>
+          <t>310243</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>317900</t>
+          <t>317903</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>319349</t>
+          <t>319963</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>331978</t>
+          <t>332136</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>634320</t>
+          <t>633765</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>647767</t>
+          <t>647909</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4377</t>
+          <t>4402</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17481</t>
+          <t>17784</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9283</t>
+          <t>9928</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24052</t>
+          <t>24773</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16231</t>
+          <t>15875</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37364</t>
+          <t>35638</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>341190</t>
+          <t>340887</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>354294</t>
+          <t>354269</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>347404</t>
+          <t>346683</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>362173</t>
+          <t>361528</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>692763</t>
+          <t>694489</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>713896</t>
+          <t>714252</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,83%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10996</t>
+          <t>10884</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>4908</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20823</t>
+          <t>18613</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8891</t>
+          <t>9028</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24528</t>
+          <t>26362</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>192312</t>
+          <t>192424</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>201572</t>
+          <t>201595</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>186845</t>
+          <t>189055</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>202349</t>
+          <t>202760</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>386448</t>
+          <t>384614</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>402085</t>
+          <t>401948</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6399</t>
+          <t>5760</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21147</t>
+          <t>20792</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5648</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19235</t>
+          <t>20804</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>268864</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>270811</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>256997</t>
+          <t>257352</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>271745</t>
+          <t>272384</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>529720</t>
+          <t>528151</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>543307</t>
+          <t>542422</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13402</t>
+          <t>12547</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30355</t>
+          <t>30537</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26609</t>
+          <t>25997</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>49664</t>
+          <t>49352</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>43887</t>
+          <t>44471</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>71645</t>
+          <t>73348</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>584672</t>
+          <t>584490</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>601625</t>
+          <t>602480</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>588555</t>
+          <t>588867</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>611610</t>
+          <t>612222</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1181601</t>
+          <t>1179898</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1209359</t>
+          <t>1208775</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,45%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>40729</t>
+          <t>39646</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>66837</t>
+          <t>66741</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>53803</t>
+          <t>53818</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>88814</t>
+          <t>87086</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>98793</t>
+          <t>101975</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>144123</t>
+          <t>142098</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,3%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>676958</t>
+          <t>677054</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>703066</t>
+          <t>704149</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>694697</t>
+          <t>696425</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>729708</t>
+          <t>729693</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1383183</t>
+          <t>1385208</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1428513</t>
+          <t>1425331</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,32%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>92695</t>
+          <t>94626</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>134837</t>
+          <t>136121</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>198422</t>
+          <t>199560</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>260679</t>
+          <t>258014</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>306644</t>
+          <t>303891</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>378429</t>
+          <t>374096</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3141706</t>
+          <t>3140422</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3183848</t>
+          <t>3181917</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3118518</t>
+          <t>3121183</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3180775</t>
+          <t>3179637</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6277312</t>
+          <t>6281645</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6349097</t>
+          <t>6351850</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,43%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas en 2012</t>
+          <t>Población con cinco o más enfermedades crónicas en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6560</t>
+          <t>7325</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21452</t>
+          <t>22308</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17180</t>
+          <t>16862</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38374</t>
+          <t>38595</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28008</t>
+          <t>27899</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53851</t>
+          <t>54222</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,32%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>273286</t>
+          <t>272430</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>288178</t>
+          <t>287413</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>248871</t>
+          <t>248650</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>270065</t>
+          <t>270383</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>528132</t>
+          <t>527761</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>553975</t>
+          <t>554084</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,21%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15647</t>
+          <t>15747</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38510</t>
+          <t>37162</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36368</t>
+          <t>37567</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64194</t>
+          <t>64809</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>58708</t>
+          <t>59519</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>92807</t>
+          <t>93805</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,11%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>467017</t>
+          <t>468365</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>489880</t>
+          <t>489780</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>459571</t>
+          <t>458956</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>487397</t>
+          <t>486198</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>936485</t>
+          <t>935487</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>970584</t>
+          <t>969773</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,22%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4015</t>
+          <t>4035</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19186</t>
+          <t>17947</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19214</t>
+          <t>19358</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41937</t>
+          <t>40436</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27009</t>
+          <t>26757</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52231</t>
+          <t>52073</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>304860</t>
+          <t>306099</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>320031</t>
+          <t>320011</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>299083</t>
+          <t>300584</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>321806</t>
+          <t>321662</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>612835</t>
+          <t>612993</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>638057</t>
+          <t>638309</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,98%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8477</t>
+          <t>8839</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24102</t>
+          <t>24773</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43702</t>
+          <t>43251</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71451</t>
+          <t>69500</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54223</t>
+          <t>55422</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>86971</t>
+          <t>90538</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>349880</t>
+          <t>349209</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>365505</t>
+          <t>365143</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>317500</t>
+          <t>319451</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>345249</t>
+          <t>345700</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>675962</t>
+          <t>672395</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>708710</t>
+          <t>707511</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,74%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10705</t>
+          <t>11090</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28503</t>
+          <t>28337</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28052</t>
+          <t>27268</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51689</t>
+          <t>51741</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>42266</t>
+          <t>44454</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>73750</t>
+          <t>75607</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,49%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>184115</t>
+          <t>184281</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>201913</t>
+          <t>201528</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>167902</t>
+          <t>167850</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>191539</t>
+          <t>192323</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>358459</t>
+          <t>356602</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>389943</t>
+          <t>387755</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>89,71%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7230</t>
+          <t>8109</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21131</t>
+          <t>22933</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11295</t>
+          <t>11316</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28282</t>
+          <t>28622</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22416</t>
+          <t>22241</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>44240</t>
+          <t>44210</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>252850</t>
+          <t>251048</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266751</t>
+          <t>265872</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>251749</t>
+          <t>251409</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>268736</t>
+          <t>268715</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>509772</t>
+          <t>509802</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>531596</t>
+          <t>531771</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,99%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13257</t>
+          <t>13149</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31965</t>
+          <t>31922</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>53523</t>
+          <t>54049</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>87472</t>
+          <t>86593</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>70600</t>
+          <t>72066</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>110343</t>
+          <t>110442</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>630823</t>
+          <t>630866</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>649531</t>
+          <t>649639</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6247,7 +6247,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>606381</t>
+          <t>607260</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>640330</t>
+          <t>639804</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1246298</t>
+          <t>1246199</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1286041</t>
+          <t>1284575</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,69%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7709</t>
+          <t>8386</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22774</t>
+          <t>23985</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>51287</t>
+          <t>52999</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>84885</t>
+          <t>83886</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>64063</t>
+          <t>65273</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>99412</t>
+          <t>100159</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>756324</t>
+          <t>755113</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>771389</t>
+          <t>770712</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>738968</t>
+          <t>739967</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>772566</t>
+          <t>770854</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1503539</t>
+          <t>1502792</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1538888</t>
+          <t>1537678</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,93%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>107465</t>
+          <t>106968</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>153734</t>
+          <t>156398</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>313531</t>
+          <t>316576</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>388151</t>
+          <t>388206</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,7 +6850,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>436314</t>
+          <t>438667</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>523549</t>
+          <t>522074</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3273045</t>
+          <t>3270381</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3319314</t>
+          <t>3319811</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3170158</t>
+          <t>3170103</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3244778</t>
+          <t>3241733</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6461539</t>
+          <t>6463014</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6548774</t>
+          <t>6546421</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,72%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas en 2016</t>
+          <t>Población con cinco o más enfermedades crónicas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7972</t>
+          <t>7665</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22696</t>
+          <t>22938</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28553</t>
+          <t>27754</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52382</t>
+          <t>52791</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40966</t>
+          <t>39291</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>70925</t>
+          <t>68648</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>11,79%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>271065</t>
+          <t>270823</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>285789</t>
+          <t>286096</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>236321</t>
+          <t>235912</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>260150</t>
+          <t>260949</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>511539</t>
+          <t>513816</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>541498</t>
+          <t>543173</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,25%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3463</t>
+          <t>3638</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14931</t>
+          <t>15124</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20560</t>
+          <t>21092</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43990</t>
+          <t>44203</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27029</t>
+          <t>27234</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>53420</t>
+          <t>52835</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>487644</t>
+          <t>487451</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>499112</t>
+          <t>498937</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>479094</t>
+          <t>478881</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>502524</t>
+          <t>501992</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>972239</t>
+          <t>972824</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>998630</t>
+          <t>998425</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,34%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2355</t>
+          <t>1677</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10996</t>
+          <t>10477</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12482</t>
+          <t>12488</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32601</t>
+          <t>31864</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16633</t>
+          <t>16719</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38432</t>
+          <t>37158</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>307569</t>
+          <t>308088</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>316210</t>
+          <t>316888</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>303708</t>
+          <t>304445</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>323827</t>
+          <t>323821</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>616442</t>
+          <t>617716</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>638241</t>
+          <t>638155</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,45%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11961</t>
+          <t>11890</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29826</t>
+          <t>29528</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38942</t>
+          <t>38855</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67105</t>
+          <t>67082</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>55094</t>
+          <t>55517</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>89828</t>
+          <t>88807</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,73%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>340138</t>
+          <t>340436</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>358003</t>
+          <t>358074</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>320178</t>
+          <t>320201</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>348341</t>
+          <t>348428</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>667419</t>
+          <t>668440</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>702153</t>
+          <t>701730</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,67%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4734</t>
+          <t>4880</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17122</t>
+          <t>17313</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15134</t>
+          <t>15275</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33054</t>
+          <t>33857</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22763</t>
+          <t>22736</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43478</t>
+          <t>45512</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>194099</t>
+          <t>193908</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>206487</t>
+          <t>206341</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>185533</t>
+          <t>184730</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>203453</t>
+          <t>203312</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>386330</t>
+          <t>384296</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>407045</t>
+          <t>407072</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,71%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4978</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17012</t>
+          <t>17712</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11198</t>
+          <t>11121</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28128</t>
+          <t>28757</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18747</t>
+          <t>18491</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38882</t>
+          <t>39780</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>246111</t>
+          <t>245411</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>258145</t>
+          <t>257992</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>244987</t>
+          <t>244358</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>261917</t>
+          <t>261994</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>497356</t>
+          <t>496458</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>517491</t>
+          <t>517747</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,55%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17858</t>
+          <t>18168</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39346</t>
+          <t>40277</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>58484</t>
+          <t>59290</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>91254</t>
+          <t>92523</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>82835</t>
+          <t>82713</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>124528</t>
+          <t>122833</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,11%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>617212</t>
+          <t>616281</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>638700</t>
+          <t>638390</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>600040</t>
+          <t>598771</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>632810</t>
+          <t>632004</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1223324</t>
+          <t>1225019</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1265017</t>
+          <t>1265139</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,86%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17893</t>
+          <t>17795</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>38234</t>
+          <t>38138</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>72442</t>
+          <t>72252</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>109715</t>
+          <t>111331</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>96221</t>
+          <t>96169</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>143059</t>
+          <t>140904</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>740349</t>
+          <t>740445</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>760690</t>
+          <t>760788</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>716452</t>
+          <t>714836</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>753725</t>
+          <t>753915</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1461691</t>
+          <t>1463846</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1508529</t>
+          <t>1508581</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,01%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>97702</t>
+          <t>99319</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>142580</t>
+          <t>143874</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>310099</t>
+          <t>312428</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>386289</t>
+          <t>390815</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>420266</t>
+          <t>422978</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>508712</t>
+          <t>509744</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3251770</t>
+          <t>3250476</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3296648</t>
+          <t>3295031</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3158253</t>
+          <t>3153727</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3234443</t>
+          <t>3232114</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6430180</t>
+          <t>6429148</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6518626</t>
+          <t>6515914</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,9%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas en 2023</t>
+          <t>Población con cinco o más enfermedades crónicas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3926</t>
+          <t>3996</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14389</t>
+          <t>14304</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12319</t>
+          <t>11886</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23599</t>
+          <t>23305</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18122</t>
+          <t>18490</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33007</t>
+          <t>33473</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>297054</t>
+          <t>297139</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>307517</t>
+          <t>307447</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>266036</t>
+          <t>266330</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>277316</t>
+          <t>277749</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>568070</t>
+          <t>567604</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>582955</t>
+          <t>582587</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,92%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20086</t>
+          <t>19303</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42337</t>
+          <t>42059</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59091</t>
+          <t>59433</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>83469</t>
+          <t>85584</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>83773</t>
+          <t>84621</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>119282</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,65%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>476053</t>
+          <t>476331</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>498304</t>
+          <t>499087</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>431500</t>
+          <t>429385</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>455878</t>
+          <t>455536</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>914077</t>
+          <t>912958</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>949586</t>
+          <t>948738</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,81%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28994</t>
+          <t>29190</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49625</t>
+          <t>48821</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>50221</t>
+          <t>50083</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>71358</t>
+          <t>71991</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>85514</t>
+          <t>84380</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>114164</t>
+          <t>114339</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,19%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>266425</t>
+          <t>267229</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>287056</t>
+          <t>286860</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>277770</t>
+          <t>277137</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>298907</t>
+          <t>299045</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>551014</t>
+          <t>550839</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>579664</t>
+          <t>580798</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,31%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23832</t>
+          <t>24452</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45222</t>
+          <t>45381</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37245</t>
+          <t>38218</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>80225</t>
+          <t>81927</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>71078</t>
+          <t>70530</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>116951</t>
+          <t>116250</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,75%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>267335</t>
+          <t>267176</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>288725</t>
+          <t>288105</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>395493</t>
+          <t>393791</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>438473</t>
+          <t>437500</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>671323</t>
+          <t>672024</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>717196</t>
+          <t>717744</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>91,05%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12126</t>
+          <t>11548</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24269</t>
+          <t>23382</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19592</t>
+          <t>20680</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50187</t>
+          <t>50413</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36046</t>
+          <t>38994</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>68311</t>
+          <t>69191</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,81%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>154473</t>
+          <t>155360</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>166616</t>
+          <t>167194</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>208592</t>
+          <t>208366</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>239187</t>
+          <t>238099</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>369210</t>
+          <t>368330</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>401475</t>
+          <t>398527</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,09%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>36800</t>
+          <t>37062</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>55205</t>
+          <t>55729</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>61546</t>
+          <t>61525</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>82119</t>
+          <t>82228</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>102884</t>
+          <t>103222</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>131335</t>
+          <t>131024</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,88%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>214431</t>
+          <t>213907</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>232836</t>
+          <t>232574</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>174937</t>
+          <t>174828</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>195510</t>
+          <t>195531</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>395357</t>
+          <t>395668</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>423808</t>
+          <t>423470</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,4%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>45252</t>
+          <t>46613</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>74465</t>
+          <t>76826</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>187449</t>
+          <t>184477</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>571307</t>
+          <t>601732</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>231564</t>
+          <t>231277</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>836972</t>
+          <t>789297</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>53,56%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>549814</t>
+          <t>547453</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>579027</t>
+          <t>577666</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>277958</t>
+          <t>247533</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>661816</t>
+          <t>664788</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>78,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>636572</t>
+          <t>684247</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1241980</t>
+          <t>1242267</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>84,3%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19844</t>
+          <t>19061</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>65615</t>
+          <t>64743</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>81954</t>
+          <t>80754</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>115015</t>
+          <t>112574</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>88407</t>
+          <t>91309</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>171277</t>
+          <t>176058</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,69%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>863105</t>
+          <t>863977</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>908876</t>
+          <t>909659</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>602716</t>
+          <t>605157</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>635777</t>
+          <t>636977</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1475175</t>
+          <t>1470394</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1558045</t>
+          <t>1555143</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,45%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>215175</t>
+          <t>214747</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>309745</t>
+          <t>311928</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>585192</t>
+          <t>584704</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1319657</t>
+          <t>1318188</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>832624</t>
+          <t>840275</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1690428</t>
+          <t>1625930</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>22,67%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3150072</t>
+          <t>3147889</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3244642</t>
+          <t>3245070</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2392623</t>
+          <t>2394092</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3127088</t>
+          <t>3127576</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5481669</t>
+          <t>5546167</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6339473</t>
+          <t>6331822</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,28%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/POLIPATOLOGIA_5-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/POLIPATOLOGIA_5-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3380</t>
+          <t>3345</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13394</t>
+          <t>13195</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9004</t>
+          <t>9871</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26001</t>
+          <t>26126</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15362</t>
+          <t>14872</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34022</t>
+          <t>33343</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>259616</t>
+          <t>259815</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>269630</t>
+          <t>269665</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>234837</t>
+          <t>234712</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>251834</t>
+          <t>250967</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>499826</t>
+          <t>500505</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>518486</t>
+          <t>518976</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,21%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8744</t>
+          <t>8107</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24968</t>
+          <t>25594</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45169</t>
+          <t>44449</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72848</t>
+          <t>73781</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>57344</t>
+          <t>58046</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>91365</t>
+          <t>90554</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,08%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>468107</t>
+          <t>467481</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>484331</t>
+          <t>484968</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>431101</t>
+          <t>430168</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>458780</t>
+          <t>459500</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>905659</t>
+          <t>906470</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>939680</t>
+          <t>938978</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,18%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>940</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8603</t>
+          <t>8335</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3276</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15449</t>
+          <t>16029</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6349</t>
+          <t>6631</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20493</t>
+          <t>20564</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>310243</t>
+          <t>310511</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>317903</t>
+          <t>317906</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>319963</t>
+          <t>319383</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>332136</t>
+          <t>331497</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>633765</t>
+          <t>633694</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>647909</t>
+          <t>647627</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,99%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4402</t>
+          <t>4352</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17784</t>
+          <t>17410</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9928</t>
+          <t>9756</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24773</t>
+          <t>24793</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15875</t>
+          <t>16081</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35638</t>
+          <t>35933</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>340887</t>
+          <t>341261</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>354269</t>
+          <t>354319</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>346683</t>
+          <t>346663</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>361528</t>
+          <t>361700</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>694489</t>
+          <t>694194</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>714252</t>
+          <t>714046</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1713</t>
+          <t>1712</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10884</t>
+          <t>10249</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4908</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18613</t>
+          <t>20051</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9028</t>
+          <t>7859</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26362</t>
+          <t>24901</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>192424</t>
+          <t>193059</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>201595</t>
+          <t>201596</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>189055</t>
+          <t>187617</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>202760</t>
+          <t>202689</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>384614</t>
+          <t>386075</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>401948</t>
+          <t>403117</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>98,09%</t>
         </is>
       </c>
     </row>
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5760</t>
+          <t>6582</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20792</t>
+          <t>21150</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>6460</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20804</t>
+          <t>19964</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>257352</t>
+          <t>256994</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>272384</t>
+          <t>271562</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>528151</t>
+          <t>528991</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>542422</t>
+          <t>542495</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12547</t>
+          <t>12409</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30537</t>
+          <t>29496</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>25997</t>
+          <t>26028</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>49352</t>
+          <t>50837</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>44471</t>
+          <t>42648</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>73348</t>
+          <t>71456</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>584490</t>
+          <t>585531</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>602480</t>
+          <t>602618</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>588867</t>
+          <t>587382</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>612222</t>
+          <t>612191</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1179898</t>
+          <t>1181790</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1208775</t>
+          <t>1210598</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,6%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>39646</t>
+          <t>40551</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>66741</t>
+          <t>67518</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>53818</t>
+          <t>54439</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>87086</t>
+          <t>89170</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>101975</t>
+          <t>101686</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>142098</t>
+          <t>141172</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>677054</t>
+          <t>676277</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>704149</t>
+          <t>703244</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>696425</t>
+          <t>694341</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>729693</t>
+          <t>729072</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1385208</t>
+          <t>1386134</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1425331</t>
+          <t>1425620</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,34%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>94626</t>
+          <t>92334</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>136121</t>
+          <t>132324</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>199560</t>
+          <t>198888</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>258014</t>
+          <t>259829</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>303891</t>
+          <t>303623</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>374096</t>
+          <t>375812</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3140422</t>
+          <t>3144219</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3181917</t>
+          <t>3184209</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3121183</t>
+          <t>3119368</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3179637</t>
+          <t>3180309</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6281645</t>
+          <t>6279929</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6351850</t>
+          <t>6352118</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,44%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7325</t>
+          <t>6686</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22308</t>
+          <t>21583</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16862</t>
+          <t>16353</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38595</t>
+          <t>38263</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27899</t>
+          <t>27633</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>54222</t>
+          <t>52703</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>272430</t>
+          <t>273155</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>287413</t>
+          <t>288052</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>248650</t>
+          <t>248982</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>270383</t>
+          <t>270892</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>527761</t>
+          <t>529280</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>554084</t>
+          <t>554350</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,25%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15747</t>
+          <t>15647</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37162</t>
+          <t>38322</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37567</t>
+          <t>36946</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64809</t>
+          <t>64474</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>59519</t>
+          <t>59612</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>93805</t>
+          <t>95193</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,25%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>468365</t>
+          <t>467205</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>489780</t>
+          <t>489880</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>458956</t>
+          <t>459291</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>486198</t>
+          <t>486819</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>935487</t>
+          <t>934099</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>969773</t>
+          <t>969680</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,21%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4035</t>
+          <t>4032</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17947</t>
+          <t>17027</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19358</t>
+          <t>19130</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40436</t>
+          <t>40518</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,47 +4792,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
+          <t>5,61%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>11,88%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>37777</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>26850</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>51361</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
           <t>5,68%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>11,86%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>37777</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>26757</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>52073</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>5,68%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>306099</t>
+          <t>307019</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>320011</t>
+          <t>320014</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>300584</t>
+          <t>300502</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>321662</t>
+          <t>321890</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,47 +4905,47 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
+          <t>94,39%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>602</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>627289</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>613705</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>638216</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
           <t>94,32%</t>
         </is>
       </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>602</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>627289</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>612993</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>638309</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>94,32%</t>
-        </is>
-      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,96%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8839</t>
+          <t>8918</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24773</t>
+          <t>24555</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43251</t>
+          <t>42000</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69500</t>
+          <t>69216</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>55422</t>
+          <t>55556</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>90538</t>
+          <t>87046</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,41%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>349209</t>
+          <t>349427</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>365143</t>
+          <t>365064</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>319451</t>
+          <t>319735</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>345700</t>
+          <t>346951</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>672395</t>
+          <t>675887</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>707511</t>
+          <t>707377</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,72%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11090</t>
+          <t>11009</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28337</t>
+          <t>27632</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27268</t>
+          <t>28777</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51741</t>
+          <t>51393</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>44454</t>
+          <t>44121</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>75607</t>
+          <t>70953</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>184281</t>
+          <t>184986</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>201528</t>
+          <t>201609</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>167850</t>
+          <t>168198</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>192323</t>
+          <t>190814</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>356602</t>
+          <t>361256</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>387755</t>
+          <t>388088</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,79%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8109</t>
+          <t>7223</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22933</t>
+          <t>21768</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11316</t>
+          <t>12255</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28622</t>
+          <t>28319</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22241</t>
+          <t>21895</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>44210</t>
+          <t>46043</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>251048</t>
+          <t>252213</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265872</t>
+          <t>266758</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>251409</t>
+          <t>251712</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>268715</t>
+          <t>267776</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>509802</t>
+          <t>507969</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>531771</t>
+          <t>532117</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,05%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13149</t>
+          <t>13117</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31922</t>
+          <t>33034</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>54049</t>
+          <t>53436</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>86593</t>
+          <t>86161</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>72066</t>
+          <t>71023</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>110442</t>
+          <t>111519</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>630866</t>
+          <t>629754</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>649639</t>
+          <t>649671</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>607260</t>
+          <t>607692</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>639804</t>
+          <t>640417</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1246199</t>
+          <t>1245122</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1284575</t>
+          <t>1285618</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,76%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8386</t>
+          <t>7563</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23985</t>
+          <t>23952</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>52999</t>
+          <t>50593</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>83886</t>
+          <t>83676</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>65273</t>
+          <t>64414</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>100159</t>
+          <t>100443</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>755113</t>
+          <t>755146</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>770712</t>
+          <t>771535</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>739967</t>
+          <t>740177</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>770854</t>
+          <t>773260</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1502792</t>
+          <t>1502508</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1537678</t>
+          <t>1538537</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,98%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>106968</t>
+          <t>107358</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>156398</t>
+          <t>155302</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>316576</t>
+          <t>318098</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>388206</t>
+          <t>393390</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>438667</t>
+          <t>439319</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>522074</t>
+          <t>528206</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3270381</t>
+          <t>3271477</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3319811</t>
+          <t>3319421</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3170103</t>
+          <t>3164919</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3241733</t>
+          <t>3240211</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6463014</t>
+          <t>6456882</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6546421</t>
+          <t>6545769</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,71%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>7899</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22938</t>
+          <t>22800</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27754</t>
+          <t>27511</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52791</t>
+          <t>52349</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39291</t>
+          <t>40551</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>68648</t>
+          <t>69427</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,92%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>270823</t>
+          <t>270961</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>286096</t>
+          <t>285862</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>235912</t>
+          <t>236354</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>260949</t>
+          <t>261192</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>513816</t>
+          <t>513037</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>543173</t>
+          <t>541913</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,04%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3638</t>
+          <t>3455</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15124</t>
+          <t>13776</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21092</t>
+          <t>19971</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44203</t>
+          <t>43192</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27234</t>
+          <t>26605</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52835</t>
+          <t>51314</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>487451</t>
+          <t>488799</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>498937</t>
+          <t>499120</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>478881</t>
+          <t>479892</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>501992</t>
+          <t>503113</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>972824</t>
+          <t>974345</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>998425</t>
+          <t>999054</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,41%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1677</t>
+          <t>1730</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10477</t>
+          <t>10110</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12488</t>
+          <t>12793</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31864</t>
+          <t>32964</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16719</t>
+          <t>17062</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37158</t>
+          <t>38551</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>308088</t>
+          <t>308455</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>316888</t>
+          <t>316835</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>304445</t>
+          <t>303345</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>323821</t>
+          <t>323516</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>617716</t>
+          <t>616323</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>638155</t>
+          <t>637812</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,39%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11890</t>
+          <t>12440</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29528</t>
+          <t>28862</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38855</t>
+          <t>38727</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67082</t>
+          <t>68328</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>55517</t>
+          <t>56949</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>88807</t>
+          <t>89341</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,8%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>340436</t>
+          <t>341102</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>358074</t>
+          <t>357524</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>320201</t>
+          <t>318955</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>348428</t>
+          <t>348556</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>668440</t>
+          <t>667906</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>701730</t>
+          <t>700298</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,48%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4880</t>
+          <t>4854</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17313</t>
+          <t>16910</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15275</t>
+          <t>15153</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33857</t>
+          <t>34002</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22736</t>
+          <t>22716</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45512</t>
+          <t>43355</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>193908</t>
+          <t>194311</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>206341</t>
+          <t>206367</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>184730</t>
+          <t>184585</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>203312</t>
+          <t>203434</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>384296</t>
+          <t>386453</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>407072</t>
+          <t>407092</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>4855</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17712</t>
+          <t>17039</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11121</t>
+          <t>10319</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28757</t>
+          <t>28011</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18491</t>
+          <t>18694</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>39780</t>
+          <t>39146</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>245411</t>
+          <t>246084</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>257992</t>
+          <t>258268</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>244358</t>
+          <t>245104</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>261994</t>
+          <t>262796</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>496458</t>
+          <t>497092</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>517747</t>
+          <t>517544</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,51%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18168</t>
+          <t>18333</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40277</t>
+          <t>38182</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>59290</t>
+          <t>58162</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>92523</t>
+          <t>90961</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>82713</t>
+          <t>85012</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>122833</t>
+          <t>124024</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>616281</t>
+          <t>618376</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>638390</t>
+          <t>638225</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>598771</t>
+          <t>600333</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>632004</t>
+          <t>633132</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1225019</t>
+          <t>1223828</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1265139</t>
+          <t>1262840</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,69%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17795</t>
+          <t>17611</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>38138</t>
+          <t>39290</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>72252</t>
+          <t>72242</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>111331</t>
+          <t>109435</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>96169</t>
+          <t>96139</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>140904</t>
+          <t>139420</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>740445</t>
+          <t>739293</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>760788</t>
+          <t>760972</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>714836</t>
+          <t>716732</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>753915</t>
+          <t>753925</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1463846</t>
+          <t>1465330</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1508581</t>
+          <t>1508611</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>99319</t>
+          <t>97806</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>143874</t>
+          <t>141994</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>312428</t>
+          <t>308721</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>390815</t>
+          <t>386225</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>422978</t>
+          <t>425038</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>509744</t>
+          <t>509279</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3250476</t>
+          <t>3252356</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3295031</t>
+          <t>3296544</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3153727</t>
+          <t>3158317</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3232114</t>
+          <t>3235821</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6429148</t>
+          <t>6429613</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6515914</t>
+          <t>6513854</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,87%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7592</t>
+          <t>7931</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3996</t>
+          <t>3873</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14304</t>
+          <t>14505</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>17255</t>
+          <t>18988</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11886</t>
+          <t>13744</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23305</t>
+          <t>25103</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>24847</t>
+          <t>26919</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18490</t>
+          <t>19759</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33473</t>
+          <t>35308</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>303851</t>
+          <t>310914</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>297139</t>
+          <t>304340</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>307447</t>
+          <t>314972</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>272380</t>
+          <t>297073</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>266330</t>
+          <t>290958</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>277749</t>
+          <t>302317</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>576230</t>
+          <t>607987</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>567604</t>
+          <t>599598</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>582587</t>
+          <t>615147</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,89%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29580</t>
+          <t>31528</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19303</t>
+          <t>21970</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42059</t>
+          <t>46257</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>70508</t>
+          <t>73960</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59433</t>
+          <t>61053</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>85584</t>
+          <t>88279</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,22 +11110,22 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>100089</t>
+          <t>105487</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>84621</t>
+          <t>88225</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>120401</t>
+          <t>124557</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -11135,7 +11135,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,56%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>488810</t>
+          <t>499119</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>476331</t>
+          <t>484390</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>499087</t>
+          <t>508677</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>444461</t>
+          <t>472534</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>429385</t>
+          <t>458215</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>455536</t>
+          <t>485441</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,27 +11223,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>933270</t>
+          <t>971654</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>912958</t>
+          <t>952584</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>948738</t>
+          <t>988916</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>38352</t>
+          <t>39561</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29190</t>
+          <t>31190</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48821</t>
+          <t>51108</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>60029</t>
+          <t>60792</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>50083</t>
+          <t>50752</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>71991</t>
+          <t>72587</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>98381</t>
+          <t>100354</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>84380</t>
+          <t>86825</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>114339</t>
+          <t>115936</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,24%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>277698</t>
+          <t>276432</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>267229</t>
+          <t>264885</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>286860</t>
+          <t>284803</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>289099</t>
+          <t>295589</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>277137</t>
+          <t>283794</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>299045</t>
+          <t>305629</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>566797</t>
+          <t>572021</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>550839</t>
+          <t>556439</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>580798</t>
+          <t>585550</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,09%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>33405</t>
+          <t>36085</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24452</t>
+          <t>26635</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45381</t>
+          <t>49081</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>62668</t>
+          <t>66908</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38218</t>
+          <t>57175</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81927</t>
+          <t>80431</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>96073</t>
+          <t>102993</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>70530</t>
+          <t>87712</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>116250</t>
+          <t>118281</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,88%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>279152</t>
+          <t>337060</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>267176</t>
+          <t>324064</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>288105</t>
+          <t>346510</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>413050</t>
+          <t>355053</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>393791</t>
+          <t>341530</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>437500</t>
+          <t>364786</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>692201</t>
+          <t>692114</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>672024</t>
+          <t>676826</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>717744</t>
+          <t>707395</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>88,97%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>17276</t>
+          <t>18140</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11548</t>
+          <t>12897</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23382</t>
+          <t>25113</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>38630</t>
+          <t>39472</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20680</t>
+          <t>32187</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50413</t>
+          <t>46676</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>57612</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>38994</t>
+          <t>48917</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>69191</t>
+          <t>67921</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>161466</t>
+          <t>187525</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>155360</t>
+          <t>180552</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>167194</t>
+          <t>192768</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>220149</t>
+          <t>189446</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>208366</t>
+          <t>182242</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>238099</t>
+          <t>196731</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>381615</t>
+          <t>376970</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>368330</t>
+          <t>366661</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>398527</t>
+          <t>385665</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>88,74%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>45665</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>37062</t>
+          <t>36194</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>55729</t>
+          <t>55747</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>71473</t>
+          <t>73621</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>61525</t>
+          <t>63494</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>82228</t>
+          <t>85453</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>117138</t>
+          <t>119421</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>103222</t>
+          <t>106432</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>131024</t>
+          <t>134001</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,07%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>223971</t>
+          <t>224907</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>213907</t>
+          <t>214960</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>232574</t>
+          <t>234513</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>185583</t>
+          <t>190129</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>174828</t>
+          <t>178297</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>195531</t>
+          <t>200256</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>409554</t>
+          <t>415036</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>395668</t>
+          <t>400456</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>423470</t>
+          <t>428025</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,09%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>58904</t>
+          <t>67465</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>46613</t>
+          <t>51992</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>76826</t>
+          <t>83697</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>352190</t>
+          <t>174948</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>184477</t>
+          <t>155142</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>601732</t>
+          <t>197016</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>411093</t>
+          <t>242413</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>231277</t>
+          <t>216153</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>789297</t>
+          <t>269643</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>18,08%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>565375</t>
+          <t>652222</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>547453</t>
+          <t>635990</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>577666</t>
+          <t>667695</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>497075</t>
+          <t>597109</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>247533</t>
+          <t>575041</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>664788</t>
+          <t>616915</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1062451</t>
+          <t>1249331</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>684247</t>
+          <t>1222101</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1242267</t>
+          <t>1275591</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>85,51%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>44462</t>
+          <t>50100</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19061</t>
+          <t>39868</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>64743</t>
+          <t>65350</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>95556</t>
+          <t>103717</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>80754</t>
+          <t>88548</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>112574</t>
+          <t>119804</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>140019</t>
+          <t>153817</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>91309</t>
+          <t>135603</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>176058</t>
+          <t>174816</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,73%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>884258</t>
+          <t>747972</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>863977</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>909659</t>
+          <t>758204</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>622175</t>
+          <t>727614</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>605157</t>
+          <t>711527</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>636977</t>
+          <t>742783</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1506433</t>
+          <t>1475586</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1470394</t>
+          <t>1454587</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1555143</t>
+          <t>1493800</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>91,68%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>275237</t>
+          <t>296611</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>214747</t>
+          <t>269188</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>311928</t>
+          <t>326031</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>768308</t>
+          <t>612406</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>584704</t>
+          <t>577420</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1318188</t>
+          <t>648180</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1043545</t>
+          <t>909017</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>840275</t>
+          <t>863262</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1625930</t>
+          <t>960896</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>13,22%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3184580</t>
+          <t>3236151</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3147889</t>
+          <t>3206731</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3245070</t>
+          <t>3263574</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2943972</t>
+          <t>3124548</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2394092</t>
+          <t>3088774</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3127576</t>
+          <t>3159534</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6128552</t>
+          <t>6360699</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5546167</t>
+          <t>6308820</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6331822</t>
+          <t>6406454</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,13%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
